--- a/Milestone docs/Unit_Test_Plan_v0.1.xlsx
+++ b/Milestone docs/Unit_Test_Plan_v0.1.xlsx
@@ -1,28 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rajas\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AI-Code-Review-Agent\Milestone docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91E0B470-A296-4253-9E7B-41312F724135}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBFC0B99-576A-4089-88E6-2F747DFCAF95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Test Results" sheetId="1" r:id="rId1"/>
+    <sheet name="UT" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="149">
-  <si>
-    <t>Sl No</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="148">
+  <si>
+    <t>Sl: No:</t>
   </si>
   <si>
     <t>Test Case Name</t>
@@ -31,7 +31,7 @@
     <t>Test Procedure</t>
   </si>
   <si>
-    <t>Condition to be Tested</t>
+    <t>Condition to be tested</t>
   </si>
   <si>
     <t>Expected Result</t>
@@ -43,193 +43,133 @@
     <t>Detect SQL Injection</t>
   </si>
   <si>
-    <t>Upload Java code with concatenated SQL query</t>
-  </si>
-  <si>
-    <t>SQL Injection present</t>
-  </si>
-  <si>
-    <t>SQL Injection detected (Critical)</t>
+    <t>Upload Java code containing concatenated SQL query</t>
+  </si>
+  <si>
+    <t>SQL Injection vulnerability present</t>
+  </si>
+  <si>
+    <t>SQL Injection detected (High)</t>
   </si>
   <si>
     <t>Pass</t>
   </si>
   <si>
-    <t>Detect Hardcoded Secret</t>
-  </si>
-  <si>
-    <t>Upload Python file containing API key</t>
+    <t>Detect Hardcoded Secrets</t>
+  </si>
+  <si>
+    <t>Upload Java/Python code containing hardcoded password or API key</t>
   </si>
   <si>
     <t>Hardcoded secret present</t>
   </si>
   <si>
-    <t>Hardcoded Secret detected</t>
-  </si>
-  <si>
-    <t>Detect Weak Password</t>
-  </si>
-  <si>
-    <t>Upload password = "123456"</t>
-  </si>
-  <si>
-    <t>Weak password present</t>
-  </si>
-  <si>
-    <t>Weak Authentication detected</t>
-  </si>
-  <si>
-    <t>Detect Unsafe eval()</t>
-  </si>
-  <si>
-    <t>Upload Python code using eval()</t>
-  </si>
-  <si>
-    <t>eval() used</t>
-  </si>
-  <si>
-    <t>Unsafe eval detected</t>
+    <t>Hardcoded Secrets detected (High)</t>
+  </si>
+  <si>
+    <t>Detect Weak Authentication</t>
+  </si>
+  <si>
+    <t>Upload Java login code using hardcoded password comparison</t>
+  </si>
+  <si>
+    <t>Weak authentication mechanism present</t>
+  </si>
+  <si>
+    <t>Weak Authentication detected (High)</t>
   </si>
   <si>
     <t>Detect Command Injection</t>
   </si>
   <si>
-    <t>Upload os.system(user_input)</t>
-  </si>
-  <si>
-    <t>Command execution present</t>
-  </si>
-  <si>
-    <t>Command Injection detected</t>
+    <t>Upload Java code using Runtime.exec(userInput) or Python os.system(user_input)</t>
+  </si>
+  <si>
+    <t>User input executed as command</t>
+  </si>
+  <si>
+    <t>Command Injection detected (Critical)</t>
+  </si>
+  <si>
+    <t>Detect Insecure Deserialization</t>
+  </si>
+  <si>
+    <t>Upload Java code using ObjectInputStream.readObject() or Python pickle.loads()</t>
+  </si>
+  <si>
+    <t>Unsafe deserialization present</t>
+  </si>
+  <si>
+    <t>Insecure Deserialization detected (High)</t>
+  </si>
+  <si>
+    <t>Detect Cross-Site Scripting (XSS)</t>
+  </si>
+  <si>
+    <t>Upload servlet or web response that prints unsanitized user input</t>
+  </si>
+  <si>
+    <t>Reflected XSS present</t>
+  </si>
+  <si>
+    <t>Cross-Site Scripting detected (Medium)</t>
+  </si>
+  <si>
+    <t>Detect Path Traversal</t>
+  </si>
+  <si>
+    <t>Upload code using user-controlled file paths</t>
+  </si>
+  <si>
+    <t>Path traversal vulnerability present</t>
+  </si>
+  <si>
+    <t>Path Traversal detected (High)</t>
   </si>
   <si>
     <t>Detect Weak Cryptography</t>
   </si>
   <si>
-    <t>Upload hashlib.md5()</t>
-  </si>
-  <si>
-    <t>Weak algorithm used</t>
-  </si>
-  <si>
-    <t>Weak Cryptography detected</t>
-  </si>
-  <si>
-    <t>Detect Cross-Site Scripting (XSS)</t>
-  </si>
-  <si>
-    <t>Upload HTML response with user input</t>
-  </si>
-  <si>
-    <t>XSS vulnerability present</t>
-  </si>
-  <si>
-    <t>XSS detected</t>
-  </si>
-  <si>
-    <t>Detect Path Traversal</t>
-  </si>
-  <si>
-    <t>Upload open("../"+filename)</t>
-  </si>
-  <si>
-    <t>Path traversal present</t>
-  </si>
-  <si>
-    <t>Path Traversal detected</t>
-  </si>
-  <si>
-    <t>Detect Insecure Deserialization</t>
-  </si>
-  <si>
-    <t>Upload pickle.loads()</t>
-  </si>
-  <si>
-    <t>Unsafe deserialization used</t>
-  </si>
-  <si>
-    <t>Insecure Deserialization detected</t>
-  </si>
-  <si>
-    <t>Detect Weak Random</t>
-  </si>
-  <si>
-    <t>Upload OTP generation using random.randint()</t>
+    <t>Upload Python code using hashlib.md5() or Java MD5 hashing</t>
+  </si>
+  <si>
+    <t>Weak cryptographic algorithm used</t>
+  </si>
+  <si>
+    <t>Weak Cryptography detected (Medium)</t>
+  </si>
+  <si>
+    <t>Detect Weak Random Number Generation</t>
+  </si>
+  <si>
+    <t>Upload code using random.randint() or java.util.Random for security tokens</t>
   </si>
   <si>
     <t>Weak random generator used</t>
   </si>
   <si>
-    <t>Weak Random Number Generation detected</t>
-  </si>
-  <si>
-    <t>Detect Cross-Site Request Forgery (CSRF)</t>
-  </si>
-  <si>
-    <t>Upload Flask/Django code without CSRF protection</t>
-  </si>
-  <si>
-    <t>Missing CSRF protection</t>
-  </si>
-  <si>
-    <t>CSRF detected</t>
-  </si>
-  <si>
-    <t>Detect Server-Side Request Forgery (SSRF)</t>
-  </si>
-  <si>
-    <t>Upload requests.get(user_input)</t>
-  </si>
-  <si>
-    <t>External URL fetched from user input</t>
-  </si>
-  <si>
-    <t>SSRF detected</t>
-  </si>
-  <si>
-    <t>Detect XML External Entity (XXE)</t>
-  </si>
-  <si>
-    <t>Upload Java XML parser with insecure configuration</t>
-  </si>
-  <si>
-    <t>XXE vulnerability present</t>
-  </si>
-  <si>
-    <t>XXE detected</t>
-  </si>
-  <si>
-    <t>Detect Weak JWT Configuration</t>
-  </si>
-  <si>
-    <t>Upload JWT code using weak secret/algorithm</t>
-  </si>
-  <si>
-    <t>Weak JWT implementation</t>
-  </si>
-  <si>
-    <t>Weak JWT detected</t>
-  </si>
-  <si>
-    <t>Detect Debug Mode</t>
-  </si>
-  <si>
-    <t>Upload app.run(debug=True)</t>
-  </si>
-  <si>
-    <t>Debug mode enabled</t>
-  </si>
-  <si>
-    <t>Debug Mode detected</t>
+    <t>Weak Random Number Generation detected (Medium)</t>
+  </si>
+  <si>
+    <t>Detect Broken Access Control</t>
+  </si>
+  <si>
+    <t>Upload Java code exposing admin functionality without authorization checks</t>
+  </si>
+  <si>
+    <t>Missing authorization validation</t>
+  </si>
+  <si>
+    <t>Broken Access Control detected (High)</t>
   </si>
   <si>
     <t>Detect Console Output (Python)</t>
   </si>
   <si>
-    <t>Upload Python code with print()</t>
-  </si>
-  <si>
-    <t>Console output used</t>
+    <t>Upload Python code containing print()</t>
+  </si>
+  <si>
+    <t>Console logging present</t>
   </si>
   <si>
     <t>Console Output detected</t>
@@ -238,13 +178,13 @@
     <t>Detect Console Output (Java)</t>
   </si>
   <si>
-    <t>Upload Java code with System.out.println()</t>
+    <t>Upload Java code containing System.out.println()</t>
   </si>
   <si>
     <t>Detect Long Line</t>
   </si>
   <si>
-    <t>Upload source code containing a line longer than 120 characters</t>
+    <t>Upload source code with a line longer than 120 characters</t>
   </si>
   <si>
     <t>Long line present</t>
@@ -256,7 +196,7 @@
     <t>Detect Long Method</t>
   </si>
   <si>
-    <t>Upload method containing more than 30 lines</t>
+    <t>Upload method exceeding configured length threshold</t>
   </si>
   <si>
     <t>Long method present</t>
@@ -271,7 +211,7 @@
     <t>Upload method with more than five parameters</t>
   </si>
   <si>
-    <t>Excessive parameters</t>
+    <t>Excessive parameters present</t>
   </si>
   <si>
     <t>Too Many Parameters detected</t>
@@ -280,7 +220,7 @@
     <t>Detect Magic Numbers</t>
   </si>
   <si>
-    <t>Upload code containing numeric literals (e.g., 99)</t>
+    <t>Upload source code containing unexplained numeric literals</t>
   </si>
   <si>
     <t>Magic number present</t>
@@ -292,13 +232,13 @@
     <t>Detect TODO/FIXME Comments</t>
   </si>
   <si>
-    <t>Upload source containing TODO/FIXME comments</t>
-  </si>
-  <si>
-    <t>Pending comments present</t>
-  </si>
-  <si>
-    <t>TODO Comment detected</t>
+    <t>Upload source containing TODO or FIXME comments</t>
+  </si>
+  <si>
+    <t>Pending development comments present</t>
+  </si>
+  <si>
+    <t>TODO/FIXME Comment detected</t>
   </si>
   <si>
     <t>Detect Duplicate Imports</t>
@@ -316,10 +256,10 @@
     <t>Detect Unused Imports</t>
   </si>
   <si>
-    <t>Upload imported module that is never used</t>
-  </si>
-  <si>
-    <t>Unused import present</t>
+    <t>Upload unused import statements</t>
+  </si>
+  <si>
+    <t>Unused imports present</t>
   </si>
   <si>
     <t>Unused Import detected</t>
@@ -328,7 +268,7 @@
     <t>Detect Global Variables</t>
   </si>
   <si>
-    <t>Upload Python code containing global variables</t>
+    <t>Upload Python code declaring global variables</t>
   </si>
   <si>
     <t>Global variable declared</t>
@@ -337,25 +277,25 @@
     <t>Global Variable detected</t>
   </si>
   <si>
-    <t>Detect Bare Except</t>
-  </si>
-  <si>
-    <t>Upload Python code with except:</t>
+    <t>Detect Bare Exception</t>
+  </si>
+  <si>
+    <t>Upload Python code using except:</t>
   </si>
   <si>
     <t>Bare exception handler present</t>
   </si>
   <si>
-    <t>Bare Except detected</t>
+    <t>Bare Exception detected</t>
   </si>
   <si>
     <t>Detect Empty Exception Block</t>
   </si>
   <si>
-    <t>Upload Python code with except: pass</t>
-  </si>
-  <si>
-    <t>Exception silently ignored</t>
+    <t>Upload Python code using except: pass</t>
+  </si>
+  <si>
+    <t>Empty exception handler present</t>
   </si>
   <si>
     <t>Empty Exception Block detected</t>
@@ -364,7 +304,7 @@
     <t>Detect Generic Exception Catch</t>
   </si>
   <si>
-    <t>Upload Java code with catch(Exception e)</t>
+    <t>Upload Java code using catch(Exception e)</t>
   </si>
   <si>
     <t>Generic exception caught</t>
@@ -376,10 +316,10 @@
     <t>Detect Possible Infinite Loop</t>
   </si>
   <si>
-    <t>Upload while True: loop</t>
-  </si>
-  <si>
-    <t>Infinite loop present</t>
+    <t>Upload Python code containing while True: without exit condition</t>
+  </si>
+  <si>
+    <t>Infinite loop possible</t>
   </si>
   <si>
     <t>Possible Infinite Loop detected</t>
@@ -388,7 +328,7 @@
     <t>Detect Deep Nesting</t>
   </si>
   <si>
-    <t>Upload nested if statements (depth ≥ 5)</t>
+    <t>Upload code with nesting depth greater than five</t>
   </si>
   <si>
     <t>Deep nesting present</t>
@@ -397,34 +337,34 @@
     <t>Deep Nesting detected</t>
   </si>
   <si>
-    <t>Detect Java File</t>
+    <t>Detect Java Source File</t>
   </si>
   <si>
     <t>Upload valid Java source file</t>
   </si>
   <si>
-    <t>Java syntax valid</t>
-  </si>
-  <si>
-    <t>Java detected successfully</t>
-  </si>
-  <si>
-    <t>Detect Python File</t>
+    <t>Java file uploaded</t>
+  </si>
+  <si>
+    <t>Java language detected successfully</t>
+  </si>
+  <si>
+    <t>Detect Python Source File</t>
   </si>
   <si>
     <t>Upload valid Python source file</t>
   </si>
   <si>
-    <t>Python syntax valid</t>
-  </si>
-  <si>
-    <t>Python detected successfully</t>
+    <t>Python file uploaded</t>
+  </si>
+  <si>
+    <t>Python language detected successfully</t>
   </si>
   <si>
     <t>Validate Java Syntax</t>
   </si>
   <si>
-    <t>Upload Java file with syntax errors</t>
+    <t>Upload Java source file containing syntax errors</t>
   </si>
   <si>
     <t>Invalid Java syntax</t>
@@ -436,7 +376,7 @@
     <t>Validate Python Syntax</t>
   </si>
   <si>
-    <t>Upload Python file with syntax errors</t>
+    <t>Upload Python source file containing syntax errors</t>
   </si>
   <si>
     <t>Invalid Python syntax</t>
@@ -445,35 +385,92 @@
     <t>Python syntax error reported</t>
   </si>
   <si>
-    <t>Auto Language Detection</t>
-  </si>
-  <si>
-    <t>Upload Java/Python source code</t>
+    <t>Automatic Language Detection</t>
+  </si>
+  <si>
+    <t>Upload Java and Python source files</t>
   </si>
   <si>
     <t>Language detection enabled</t>
   </si>
   <si>
-    <t>Correct language detected</t>
-  </si>
-  <si>
-    <t>Consolidated Review Report</t>
+    <t>Correct programming language identified</t>
+  </si>
+  <si>
+    <t>Generate Consolidated Review Report</t>
+  </si>
+  <si>
+    <t>Upload source code containing multiple issues</t>
+  </si>
+  <si>
+    <t>Multiple quality and security findings present</t>
+  </si>
+  <si>
+    <t>Combined report generated with severity classification and recommendations</t>
+  </si>
+  <si>
+    <t>Generate AI Remediation Suggestions</t>
   </si>
   <si>
     <t>Upload vulnerable source code</t>
   </si>
   <si>
-    <t>Multiple findings present</t>
-  </si>
-  <si>
-    <t>Combined report generated with severity and recommendations</t>
+    <t>Security findings detected</t>
+  </si>
+  <si>
+    <t>AI-generated remediation suggestions produced</t>
+  </si>
+  <si>
+    <t>Generate Pull Request Summary</t>
+  </si>
+  <si>
+    <t>Upload source code with detected findings</t>
+  </si>
+  <si>
+    <t>Analysis completed</t>
+  </si>
+  <si>
+    <t>Pull Request summary generated successfully</t>
+  </si>
+  <si>
+    <t>Retrieve Secure Coding Guidance (RAG)</t>
+  </si>
+  <si>
+    <t>Ask security-related question through AI Assistant</t>
+  </si>
+  <si>
+    <t>Knowledge base available</t>
+  </si>
+  <si>
+    <t>Relevant OWASP guidance retrieved</t>
+  </si>
+  <si>
+    <t>Generate PDF Report</t>
+  </si>
+  <si>
+    <t>Analyze vulnerable source code and export report</t>
+  </si>
+  <si>
+    <t>PDF report generated successfully</t>
+  </si>
+  <si>
+    <t>End-to-End Multi-Agent Analysis</t>
+  </si>
+  <si>
+    <t>Upload vulnerable Java/Python source code</t>
+  </si>
+  <si>
+    <t>Complete analysis pipeline executed</t>
+  </si>
+  <si>
+    <t>Language detection, syntax validation, code quality analysis, security analysis, AI remediation, PR summary, and PDF report completed successfully</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -485,27 +482,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Segoe UI"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Segoe UI"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF166534"/>
-      <name val="Segoe UI"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -514,26 +498,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8FAFC"/>
-        <bgColor rgb="FFF8FAFC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDCFCE7"/>
-        <bgColor rgb="FFDCFCE7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor rgb="FF1E293B"/>
+        <fgColor rgb="FF7B8EA5"/>
+        <bgColor rgb="FF7B8EA5"/>
       </patternFill>
     </fill>
   </fills>
@@ -547,16 +513,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFCBD5E1"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color rgb="FFCBD5E1"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color rgb="FFCBD5E1"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFCBD5E1"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -564,28 +530,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -890,751 +847,751 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F37"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="35" customWidth="1"/>
-    <col min="3" max="3" width="45" customWidth="1"/>
-    <col min="4" max="4" width="35" customWidth="1"/>
-    <col min="5" max="5" width="45" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="81.88671875" customWidth="1"/>
+    <col min="4" max="4" width="48.6640625" customWidth="1"/>
+    <col min="5" max="5" width="53.5546875" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:6" ht="28.05" customHeight="1">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
+    <row r="2" spans="1:6" ht="19.95" customHeight="1">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="4" t="s">
         <v>9</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4">
+    <row r="3" spans="1:6" ht="19.95" customHeight="1">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
+    <row r="4" spans="1:6" ht="19.95" customHeight="1">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="4" t="s">
         <v>18</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
+    <row r="5" spans="1:6" ht="19.95" customHeight="1">
+      <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
+    <row r="6" spans="1:6" ht="19.95" customHeight="1">
+      <c r="A6" s="3">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="4" t="s">
         <v>26</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="4">
+    <row r="7" spans="1:6" ht="19.95" customHeight="1">
+      <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
+    <row r="8" spans="1:6" ht="19.95" customHeight="1">
+      <c r="A8" s="3">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
+    <row r="9" spans="1:6" ht="19.95" customHeight="1">
+      <c r="A9" s="3">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="4" t="s">
         <v>38</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="1">
+    <row r="10" spans="1:6" ht="19.95" customHeight="1">
+      <c r="A10" s="3">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="4" t="s">
         <v>42</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="4">
-        <v>10</v>
-      </c>
-      <c r="B11" s="5" t="s">
+    <row r="11" spans="1:6" ht="19.95" customHeight="1">
+      <c r="A11" s="3">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="4" t="s">
         <v>46</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="1">
+    <row r="12" spans="1:6" ht="19.95" customHeight="1">
+      <c r="A12" s="3">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="4" t="s">
         <v>50</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="4">
+    <row r="13" spans="1:6" ht="19.95" customHeight="1">
+      <c r="A13" s="3">
         <v>12</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="19.95" customHeight="1">
+      <c r="A14" s="3">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="F13" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="1">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="s">
+      <c r="D14" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="E14" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="F14" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="19.95" customHeight="1">
+      <c r="A15" s="3">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="C15" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="4">
-        <v>14</v>
-      </c>
-      <c r="B15" s="5" t="s">
+      <c r="D15" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="E15" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="F15" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="19.95" customHeight="1">
+      <c r="A16" s="3">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="F15" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="1">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2" t="s">
+      <c r="D16" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="E16" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="F16" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="19.95" customHeight="1">
+      <c r="A17" s="3">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="C17" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="F16" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>16</v>
-      </c>
-      <c r="B17" s="5" t="s">
+      <c r="D17" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="E17" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="F17" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="19.95" customHeight="1">
+      <c r="A18" s="3">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="F17" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="1">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2" t="s">
+      <c r="D18" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="E18" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="F18" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="4">
+    <row r="19" spans="1:6" ht="19.95" customHeight="1">
+      <c r="A19" s="3">
         <v>18</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="4" t="s">
         <v>76</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="1">
+    <row r="20" spans="1:6" ht="19.95" customHeight="1">
+      <c r="A20" s="3">
         <v>19</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
+    <row r="21" spans="1:6" ht="19.95" customHeight="1">
+      <c r="A21" s="3">
         <v>20</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="4" t="s">
         <v>84</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="1">
+    <row r="22" spans="1:6" ht="19.95" customHeight="1">
+      <c r="A22" s="3">
         <v>21</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E22" s="4" t="s">
         <v>88</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="4">
+    <row r="23" spans="1:6" ht="19.95" customHeight="1">
+      <c r="A23" s="3">
         <v>22</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D23" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="E23" s="4" t="s">
         <v>92</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="1">
+    <row r="24" spans="1:6" ht="19.95" customHeight="1">
+      <c r="A24" s="3">
         <v>23</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E24" s="4" t="s">
         <v>96</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="4">
+    <row r="25" spans="1:6" ht="19.95" customHeight="1">
+      <c r="A25" s="3">
         <v>24</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="D25" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="E25" s="4" t="s">
         <v>100</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="1">
+    <row r="26" spans="1:6" ht="19.95" customHeight="1">
+      <c r="A26" s="3">
         <v>25</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E26" s="4" t="s">
         <v>104</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="4">
+    <row r="27" spans="1:6" ht="19.95" customHeight="1">
+      <c r="A27" s="3">
         <v>26</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="D27" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="E27" s="4" t="s">
         <v>108</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="1">
+    <row r="28" spans="1:6" ht="19.95" customHeight="1">
+      <c r="A28" s="3">
         <v>27</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E28" s="4" t="s">
         <v>112</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="4">
+    <row r="29" spans="1:6" ht="19.95" customHeight="1">
+      <c r="A29" s="3">
         <v>28</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="D29" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="E29" s="4" t="s">
         <v>116</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="1">
+    <row r="30" spans="1:6" ht="19.95" customHeight="1">
+      <c r="A30" s="3">
         <v>29</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="E30" s="4" t="s">
         <v>120</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="4">
+    <row r="31" spans="1:6" ht="19.95" customHeight="1">
+      <c r="A31" s="3">
         <v>30</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="D31" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="E31" s="4" t="s">
         <v>124</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="1">
+    <row r="32" spans="1:6" ht="19.95" customHeight="1">
+      <c r="A32" s="3">
         <v>31</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D32" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="E32" s="4" t="s">
         <v>128</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="4">
+    <row r="33" spans="1:6" ht="19.95" customHeight="1">
+      <c r="A33" s="3">
         <v>32</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="D33" s="5" t="s">
+      <c r="D33" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="5" t="s">
+      <c r="E33" s="4" t="s">
         <v>132</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="1">
+    <row r="34" spans="1:6" ht="19.95" customHeight="1">
+      <c r="A34" s="3">
         <v>33</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D34" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="E34" s="4" t="s">
         <v>136</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="4">
+    <row r="35" spans="1:6" ht="19.95" customHeight="1">
+      <c r="A35" s="3">
         <v>34</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="C35" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="D35" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="E35" s="5" t="s">
+      <c r="E35" s="4" t="s">
         <v>140</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="1">
+    <row r="36" spans="1:6" ht="19.95" customHeight="1">
+      <c r="A36" s="3">
         <v>35</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="D36" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="E36" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="F36" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="19.95" customHeight="1">
+      <c r="A37" s="3">
+        <v>36</v>
+      </c>
+      <c r="B37" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="F36" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="4">
-        <v>36</v>
-      </c>
-      <c r="B37" s="5" t="s">
+      <c r="C37" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="D37" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="D37" s="5" t="s">
+      <c r="E37" s="4" t="s">
         <v>147</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>148</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>10</v>
